--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104684_W26.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104684_W26.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0107</v>
+        <v>6.9321</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1493</v>
+        <v>6.9409</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1386</v>
+        <v>-0.0089</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3173</v>
+        <v>3.3017</v>
       </c>
       <c r="H2" t="n">
-        <v>4.4101</v>
+        <v>4.3842</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.0928</v>
+        <v>-1.0825</v>
       </c>
       <c r="J2" t="n">
-        <v>5.5388</v>
+        <v>5.4932</v>
       </c>
       <c r="K2" t="n">
-        <v>6.064</v>
+        <v>6.0222</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5251</v>
+        <v>-0.529</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.2215</v>
+        <v>-2.1915</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.6539</v>
+        <v>-1.638</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5676</v>
+        <v>-0.5535</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6403</v>
+        <v>0.5911</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8257</v>
+        <v>0.6848</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1854</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>3.0531</v>
+        <v>3.0392</v>
       </c>
       <c r="W2" t="n">
-        <v>3.0531</v>
+        <v>3.0392</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3065</v>
+        <v>5.6392</v>
       </c>
       <c r="E3" t="n">
-        <v>6.7776</v>
+        <v>7.8168</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.471</v>
+        <v>-2.1776</v>
       </c>
       <c r="G3" t="n">
-        <v>4.9177</v>
+        <v>4.9077</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8369</v>
+        <v>0.8386</v>
       </c>
       <c r="I3" t="n">
-        <v>4.0808</v>
+        <v>4.0691</v>
       </c>
       <c r="J3" t="n">
-        <v>6.2515</v>
+        <v>6.2109</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1921</v>
+        <v>2.1751</v>
       </c>
       <c r="L3" t="n">
-        <v>4.0594</v>
+        <v>4.0358</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3338</v>
+        <v>-1.3032</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3552</v>
+        <v>-1.3365</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0214</v>
+        <v>0.0333</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.7868</v>
+        <v>-0.4553</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.113</v>
+        <v>-0.0283</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6739000000000001</v>
+        <v>-0.427</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. DUBLJEVIC</t>
+          <t>J. WRIGHT-FOREMAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9642</v>
+        <v>3.2752</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4268</v>
+        <v>2.4542</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4627</v>
+        <v>0.821</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.4507</v>
+        <v>2.7572</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2829</v>
+        <v>0.9173</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1679</v>
+        <v>1.8399</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6294</v>
+        <v>2.4526</v>
       </c>
       <c r="K4" t="n">
-        <v>0.07240000000000001</v>
+        <v>1.4921</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.9605</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0801</v>
+        <v>0.3046</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3552</v>
+        <v>-0.5749</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7249</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5076</v>
+        <v>0.1522</v>
       </c>
       <c r="T4" t="n">
-        <v>1.612</v>
+        <v>-0.3139</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8955</v>
+        <v>0.4661</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0927</v>
+        <v>-0.5447</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1853</v>
+        <v>0.3155</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. WRIGHT-FOREMAN</t>
+          <t>B. DUBLJEVIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4671</v>
+        <v>2.4717</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7091</v>
+        <v>3.5519</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7581</v>
+        <v>-1.0801</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7707</v>
+        <v>-1.4389</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9368</v>
+        <v>-1.2783</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8339</v>
+        <v>-0.1606</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4874</v>
+        <v>0.6091</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5199</v>
+        <v>0.0582</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9675</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2833</v>
+        <v>-2.048</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5831</v>
+        <v>-1.3365</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8663999999999999</v>
+        <v>-0.7114</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3354</v>
+        <v>1.0001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0998</v>
+        <v>0.7638</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4352</v>
+        <v>0.2363</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5463</v>
+        <v>1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3214</v>
+        <v>2.1789</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8678</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3404</v>
+        <v>1.8883</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6502</v>
+        <v>2.3521</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3098</v>
+        <v>-0.4638</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.985</v>
+        <v>-0.9806</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0548</v>
+        <v>-0.0573</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9302</v>
+        <v>-0.9233</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0743</v>
+        <v>1.0517</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5919</v>
+        <v>0.5753</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4824</v>
+        <v>0.4764</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0593</v>
+        <v>-2.0323</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.4126</v>
+        <v>-1.3997</v>
       </c>
       <c r="P6" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1282</v>
+        <v>0.4136</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6775</v>
+        <v>0.0531</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5492</v>
+        <v>0.3605</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>Y. TRAORE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5989</v>
+        <v>0.5384</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5092</v>
+        <v>0.2555</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9103</v>
+        <v>0.2829</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7144</v>
+        <v>0.362</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3838</v>
+        <v>0.362</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3306</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6634</v>
+        <v>0.5343</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5888</v>
+        <v>0.5343</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0746</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.051</v>
+        <v>-0.1724</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.205</v>
+        <v>-0.1724</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2559</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1379</v>
+        <v>-0.2788</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2994</v>
+        <v>-0.2788</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1615</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Y. TRAORE</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5391</v>
+        <v>0.3807</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2586</v>
+        <v>1.1516</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2805</v>
+        <v>-0.7709</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3637</v>
+        <v>0.7186</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3637</v>
+        <v>0.3848</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.3338</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.6605</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5861</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.0745</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1732</v>
+        <v>0.0581</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1732</v>
+        <v>-0.2012</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.2593</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2782</v>
+        <v>-0.0907</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2782</v>
+        <v>-0.0536</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.037</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. KOUMADJE</t>
+          <t>J. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3197</v>
+        <v>0.0214</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4526</v>
+        <v>0.6092</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1329</v>
+        <v>-0.5878</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3865</v>
+        <v>-2.5013</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2612</v>
+        <v>-0.2697</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-2.2316</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1039</v>
+        <v>-0.0794</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1039</v>
+        <v>1.0235</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-1.1029</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4904</v>
+        <v>-2.4219</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1573</v>
+        <v>-1.2932</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-1.1287</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7473</v>
+        <v>0.2056</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5777</v>
+        <v>0.1925</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1697</v>
+        <v>0.013</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ</t>
+          <t>C. KOUMADJE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7366</v>
+        <v>-0.5829</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1513</v>
+        <v>-0.6911</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5853</v>
+        <v>0.1082</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4938</v>
+        <v>-0.382</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2654</v>
+        <v>0.2613</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2284</v>
+        <v>-0.6433</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0482</v>
+        <v>0.1034</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0421</v>
+        <v>0.1034</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.0903</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.4457</v>
+        <v>-0.4854</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3075</v>
+        <v>0.1579</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1381</v>
+        <v>-0.6433</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8147</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5622</v>
+        <v>0.4819</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6079</v>
+        <v>0.3436</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0457</v>
+        <v>0.1383</v>
       </c>
       <c r="V10" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5923</v>
+        <v>-1.5284</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8559</v>
+        <v>-0.8593</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7364000000000001</v>
+        <v>-0.6691</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3145</v>
+        <v>-0.3159</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4718</v>
+        <v>-0.4738</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1312,22 +1312,22 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1851</v>
+        <v>-0.1231</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1155</v>
+        <v>-0.0534</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6647</v>
+        <v>-2.1221</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2302</v>
+        <v>-0.2562</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8949</v>
+        <v>-1.8659</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.5802</v>
+        <v>-1.5749</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.212</v>
+        <v>-2.2143</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6318</v>
+        <v>0.6394</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3686</v>
+        <v>-0.3859</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.0776</v>
+        <v>-1.0934</v>
       </c>
       <c r="L12" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2116</v>
+        <v>-1.189</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1344</v>
+        <v>-1.1209</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4204</v>
+        <v>-0.0512</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5989</v>
+        <v>0.1297</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1785</v>
+        <v>-0.1808</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="13">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.5959</v>
+        <v>-3.5628</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3776</v>
+        <v>-2.7118</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2184</v>
+        <v>-0.851</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.5984</v>
+        <v>-1.6105</v>
       </c>
       <c r="H13" t="n">
-        <v>1.8989</v>
+        <v>1.9012</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.4973</v>
+        <v>-3.5117</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3441</v>
+        <v>-0.3794</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5456</v>
+        <v>2.5338</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.8896</v>
+        <v>-2.9132</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.2543</v>
+        <v>-1.231</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4097</v>
+        <v>-0.3589</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7652</v>
+        <v>-0.0561</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6445</v>
+        <v>-0.3028</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>12.3177</v>
+        <v>13.3508</v>
       </c>
       <c r="E14" t="n">
-        <v>19.8736</v>
+        <v>20.6138</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.555899999999999</v>
+        <v>-7.263</v>
       </c>
       <c r="G14" t="n">
-        <v>3.274699999999999</v>
+        <v>3.243100000000002</v>
       </c>
       <c r="H14" t="n">
-        <v>5.4336</v>
+        <v>5.387699999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.159</v>
+        <v>-2.1446</v>
       </c>
       <c r="J14" t="n">
-        <v>15.7382</v>
+        <v>15.4814</v>
       </c>
       <c r="K14" t="n">
-        <v>14.1799</v>
+        <v>14.0106</v>
       </c>
       <c r="L14" t="n">
-        <v>1.5585</v>
+        <v>1.4709</v>
       </c>
       <c r="M14" t="n">
-        <v>-12.4638</v>
+        <v>-12.2382</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.746300000000002</v>
+        <v>-8.623000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.7176</v>
+        <v>-3.6151</v>
       </c>
       <c r="P14" t="n">
-        <v>6.805099999999999</v>
+        <v>6.8291</v>
       </c>
       <c r="Q14" t="n">
-        <v>-6.805</v>
+        <v>-6.829000000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>13.6101</v>
+        <v>13.6581</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4386999999999999</v>
+        <v>1.4865</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3024999999999999</v>
+        <v>1.3671</v>
       </c>
       <c r="U14" t="n">
-        <v>0.136</v>
+        <v>0.1195</v>
       </c>
       <c r="V14" t="n">
-        <v>1.799700000000001</v>
+        <v>1.792</v>
       </c>
       <c r="W14" t="n">
-        <v>10.6375</v>
+        <v>10.5939</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.837999999999999</v>
+        <v>-8.802200000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1719</v>
+        <v>3.289</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9624</v>
+        <v>4.7858</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7905</v>
+        <v>-1.4968</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8384</v>
+        <v>1.8344</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.5757</v>
+        <v>-2.5762</v>
       </c>
       <c r="I15" t="n">
-        <v>4.4141</v>
+        <v>4.4106</v>
       </c>
       <c r="J15" t="n">
-        <v>5.1735</v>
+        <v>5.131</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.496</v>
+        <v>-0.5213</v>
       </c>
       <c r="L15" t="n">
-        <v>5.6694</v>
+        <v>5.6523</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.335</v>
+        <v>-3.2966</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.0797</v>
+        <v>-2.0549</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2554</v>
+        <v>-1.2417</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0989</v>
+        <v>0.2334</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4597</v>
+        <v>0.3456</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3608</v>
+        <v>-0.1122</v>
       </c>
       <c r="V15" t="n">
-        <v>3.5029</v>
+        <v>3.4976</v>
       </c>
       <c r="W15" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. DIAGNE</t>
+          <t>D. GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0294</v>
+        <v>1.5015</v>
       </c>
       <c r="E16" t="n">
-        <v>5.5678</v>
+        <v>2.4922</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.5384</v>
+        <v>-0.9906</v>
       </c>
       <c r="G16" t="n">
-        <v>3.6988</v>
+        <v>1.3885</v>
       </c>
       <c r="H16" t="n">
-        <v>3.3362</v>
+        <v>1.3808</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3626</v>
+        <v>0.0077</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8994</v>
+        <v>3.1206</v>
       </c>
       <c r="K16" t="n">
-        <v>4.6755</v>
+        <v>2.0857</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2239</v>
+        <v>1.035</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2007</v>
+        <v>-1.7321</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3393</v>
+        <v>-0.7048</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1387</v>
+        <v>-1.0273</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6805</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7429</v>
+        <v>0.1617</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8026</v>
+        <v>0.0136</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9403</v>
+        <v>0.1481</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.7317</v>
+        <v>1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.7317</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. PAULI</t>
+          <t>A. DIAGNE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1985</v>
+        <v>1.4623</v>
       </c>
       <c r="E17" t="n">
-        <v>3.5264</v>
+        <v>4.2476</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3279</v>
+        <v>-2.7853</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1856</v>
+        <v>3.7016</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.5613</v>
+        <v>3.3319</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3758</v>
+        <v>0.3697</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9823</v>
+        <v>4.8774</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4707</v>
+        <v>4.654</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.2234</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1679</v>
+        <v>-1.1758</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.032</v>
+        <v>-1.3221</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1359</v>
+        <v>0.1463</v>
       </c>
       <c r="P17" t="n">
-        <v>1.361</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4552</v>
+        <v>1.1673</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1875</v>
+        <v>0.5084</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2677</v>
+        <v>0.6589</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4783</v>
+        <v>-2.7237</v>
       </c>
       <c r="W17" t="n">
-        <v>2.7317</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2534</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. GARCIA</t>
+          <t>O. PAULI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0669</v>
+        <v>1.3134</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8126</v>
+        <v>3.6012</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7456</v>
+        <v>-2.2878</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3719</v>
+        <v>-1.1909</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3692</v>
+        <v>-1.5569</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0027</v>
+        <v>0.366</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1375</v>
+        <v>0.9453</v>
       </c>
       <c r="K18" t="n">
-        <v>2.0953</v>
+        <v>0.4547</v>
       </c>
       <c r="L18" t="n">
-        <v>1.0422</v>
+        <v>0.4906</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7656</v>
+        <v>-2.1362</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7261</v>
+        <v>-2.0116</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0395</v>
+        <v>-0.1246</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2634</v>
+        <v>-0.3379</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6956</v>
+        <v>-0.0678</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4322</v>
+        <v>-0.2702</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0927</v>
+        <v>1.4764</v>
       </c>
       <c r="W18" t="n">
-        <v>1.639</v>
+        <v>2.7237</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5463</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. SANZ</t>
+          <t>C. WALDEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0621</v>
+        <v>-0.6171</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.3967</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0062</v>
+        <v>-1.0138</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1272</v>
+        <v>0.0428</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2396</v>
+        <v>-0.1523</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8875999999999999</v>
+        <v>0.1952</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3205</v>
+        <v>0.0717</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3912</v>
+        <v>0.0345</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7117</v>
+        <v>0.0372</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8066</v>
+        <v>-0.0289</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6308</v>
+        <v>-0.1868</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1759</v>
+        <v>0.1579</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.7702</v>
+        <v>0.2717</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1039</v>
+        <v>0.1672</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6663</v>
+        <v>0.1046</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. WALDEN</t>
+          <t>M. SANZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9196</v>
+        <v>-0.8524</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1631</v>
+        <v>0.2243</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0827</v>
+        <v>-1.0767</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0402</v>
+        <v>-1.1204</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1544</v>
+        <v>-0.2357</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1946</v>
+        <v>-0.8847</v>
       </c>
       <c r="J20" t="n">
-        <v>0.07199999999999999</v>
+        <v>-0.3327</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0346</v>
+        <v>0.3825</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0373</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0318</v>
+        <v>-0.7877</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1891</v>
+        <v>-0.6182</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1573</v>
+        <v>-0.1695</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0278</v>
+        <v>0.9721</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0696</v>
+        <v>0.3992</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0417</v>
+        <v>0.5729</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2831</v>
+        <v>-1.6211</v>
       </c>
       <c r="E21" t="n">
-        <v>0.386</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6691</v>
+        <v>-1.5303</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6992</v>
+        <v>-0.6908</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8139</v>
+        <v>-0.8101</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1147</v>
+        <v>0.1194</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1403</v>
+        <v>-0.1464</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2149</v>
+        <v>-0.2208</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.5444</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O21" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4912</v>
+        <v>-0.8408</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5263</v>
+        <v>0.0556</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0174</v>
+        <v>-0.8964</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5749</v>
+        <v>-2.0235</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.654</v>
+        <v>-0.4419</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9209</v>
+        <v>-1.5816</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2432</v>
+        <v>0.245</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7879</v>
+        <v>-1.7838</v>
       </c>
       <c r="I22" t="n">
-        <v>2.0311</v>
+        <v>2.0288</v>
       </c>
       <c r="J22" t="n">
-        <v>1.9985</v>
+        <v>1.9815</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3219</v>
+        <v>0.3135</v>
       </c>
       <c r="L22" t="n">
-        <v>1.6765</v>
+        <v>1.668</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7552</v>
+        <v>-1.7365</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.1098</v>
+        <v>-2.0973</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0449</v>
+        <v>-0.4961</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.747</v>
+        <v>-0.5113</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2979</v>
+        <v>0.0152</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.926</v>
+        <v>-3.9139</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8828</v>
+        <v>-1.2227</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.0432</v>
+        <v>-2.6911</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.6279</v>
+        <v>-2.6294</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0982</v>
+        <v>-0.0922</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.5296</v>
+        <v>-2.5371</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7745</v>
+        <v>-0.8090000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>1.7765</v>
+        <v>1.7614</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.5511</v>
+        <v>-2.5704</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8533</v>
+        <v>-1.8203</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.8747</v>
+        <v>-1.8536</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0214</v>
+        <v>0.0333</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2567</v>
+        <v>-0.2358</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0253</v>
+        <v>-0.3163</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2314</v>
+        <v>0.0805</v>
       </c>
       <c r="V23" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W23" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.189</v>
+        <v>-4.5822</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.548</v>
+        <v>-3.222</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.641</v>
+        <v>-1.3602</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.5942</v>
+        <v>-1.5892</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2902</v>
+        <v>-1.276</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3039</v>
+        <v>-0.3132</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3935</v>
+        <v>-0.4134</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3637</v>
+        <v>0.362</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7572</v>
+        <v>-0.7754</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2007</v>
+        <v>-1.1758</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.6539</v>
+        <v>-1.638</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6875</v>
+        <v>-0.0825</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8861</v>
+        <v>-0.5323</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1987</v>
+        <v>0.4498</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.8299</v>
+        <v>-5.4717</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.7219</v>
+        <v>-3.5073</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.1081</v>
+        <v>-1.9645</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.2329</v>
+        <v>-3.2348</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.6176</v>
+        <v>-1.617</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.6153</v>
+        <v>-1.6178</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.1703</v>
+        <v>-2.1878</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.6722</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.4981</v>
+        <v>-1.5048</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.0626</v>
+        <v>-1.0471</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.9453</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8239</v>
+        <v>-0.4645</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4174</v>
+        <v>-0.1813</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4065</v>
+        <v>-0.2832</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-12.3179</v>
+        <v>-11.5157</v>
       </c>
       <c r="E26" t="n">
-        <v>7.555700000000002</v>
+        <v>7.263100000000002</v>
       </c>
       <c r="F26" t="n">
-        <v>-19.8736</v>
+        <v>-18.7787</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.2745</v>
+        <v>-3.243199999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>-5.4334</v>
+        <v>-5.3875</v>
       </c>
       <c r="I26" t="n">
-        <v>2.1592</v>
+        <v>2.1446</v>
       </c>
       <c r="J26" t="n">
-        <v>12.4641</v>
+        <v>12.2382</v>
       </c>
       <c r="K26" t="n">
-        <v>8.7463</v>
+        <v>8.623200000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>3.7174</v>
+        <v>3.615200000000002</v>
       </c>
       <c r="M26" t="n">
-        <v>-15.7384</v>
+        <v>-15.4814</v>
       </c>
       <c r="N26" t="n">
-        <v>-14.1797</v>
+        <v>-14.0106</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.5587</v>
+        <v>-1.4707</v>
       </c>
       <c r="P26" t="n">
-        <v>-6.805000000000001</v>
+        <v>-6.829000000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>-13.61</v>
+        <v>-13.658</v>
       </c>
       <c r="R26" t="n">
-        <v>6.805199999999999</v>
+        <v>6.8292</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.4385999999999995</v>
+        <v>0.3485999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1360000000000005</v>
+        <v>-0.1193999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3025000000000002</v>
+        <v>0.4680000000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.7999</v>
+        <v>-1.7921</v>
       </c>
       <c r="W26" t="n">
-        <v>8.837900000000001</v>
+        <v>8.802199999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>-10.6377</v>
+        <v>-10.5941</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104684_W26.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104684_W26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104684_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104684_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104684_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104684_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104684_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104684_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104684_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104684_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104684_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104684_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104684_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104684_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-8.802200000000001</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104684_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104684_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104684_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104684_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104684_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104684_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104684_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104684_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104684_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104684_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104684_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-10.5941</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
